--- a/LoanOfficer-A/2026/162 angom bijenty.xlsx
+++ b/LoanOfficer-A/2026/162 angom bijenty.xlsx
@@ -819,7 +819,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>1500</v>
+        <v>7500</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>58500</v>
+        <v>52500</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -970,9 +970,15 @@
       <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="1"/>
+      <c r="B6" s="3">
+        <v>46093</v>
+      </c>
+      <c r="C6" s="4">
+        <v>500</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
       <c r="E6" s="1">
         <v>34</v>
       </c>
@@ -996,9 +1002,15 @@
       <c r="A7" s="1">
         <v>5</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="1"/>
+      <c r="B7" s="3">
+        <v>46094</v>
+      </c>
+      <c r="C7" s="4">
+        <v>500</v>
+      </c>
+      <c r="D7" s="1">
+        <v>1</v>
+      </c>
       <c r="E7" s="1">
         <v>35</v>
       </c>
@@ -1022,9 +1034,15 @@
       <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="1"/>
+      <c r="B8" s="3">
+        <v>46095</v>
+      </c>
+      <c r="C8" s="4">
+        <v>500</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
       <c r="E8" s="1">
         <v>36</v>
       </c>
@@ -1048,9 +1066,15 @@
       <c r="A9" s="1">
         <v>7</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="1"/>
+      <c r="B9" s="3">
+        <v>46098</v>
+      </c>
+      <c r="C9" s="4">
+        <v>500</v>
+      </c>
+      <c r="D9" s="1">
+        <v>1</v>
+      </c>
       <c r="E9" s="1">
         <v>37</v>
       </c>
@@ -1074,9 +1098,15 @@
       <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="1"/>
+      <c r="B10" s="3">
+        <v>46099</v>
+      </c>
+      <c r="C10" s="4">
+        <v>500</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
       <c r="E10" s="1">
         <v>38</v>
       </c>
@@ -1100,9 +1130,15 @@
       <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="1"/>
+      <c r="B11" s="3">
+        <v>46101</v>
+      </c>
+      <c r="C11" s="4">
+        <v>500</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
       <c r="E11" s="1">
         <v>39</v>
       </c>
@@ -1126,9 +1162,15 @@
       <c r="A12" s="1">
         <v>10</v>
       </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="1"/>
+      <c r="B12" s="3">
+        <v>46103</v>
+      </c>
+      <c r="C12" s="4">
+        <v>500</v>
+      </c>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
       <c r="E12" s="1">
         <v>40</v>
       </c>
@@ -1152,9 +1194,15 @@
       <c r="A13" s="1">
         <v>11</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="1"/>
+      <c r="B13" s="3">
+        <v>46104</v>
+      </c>
+      <c r="C13" s="4">
+        <v>500</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
       <c r="E13" s="1">
         <v>41</v>
       </c>
@@ -1177,9 +1225,15 @@
       <c r="A14" s="1">
         <v>12</v>
       </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="1"/>
+      <c r="B14" s="3">
+        <v>46106</v>
+      </c>
+      <c r="C14" s="4">
+        <v>500</v>
+      </c>
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
       <c r="E14" s="1">
         <v>42</v>
       </c>
@@ -1203,9 +1257,15 @@
       <c r="A15" s="1">
         <v>13</v>
       </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="1"/>
+      <c r="B15" s="3">
+        <v>46108</v>
+      </c>
+      <c r="C15" s="4">
+        <v>500</v>
+      </c>
+      <c r="D15" s="1">
+        <v>1</v>
+      </c>
       <c r="E15" s="1">
         <v>43</v>
       </c>
@@ -1229,9 +1289,15 @@
       <c r="A16" s="1">
         <v>14</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="1"/>
+      <c r="B16" s="3">
+        <v>46110</v>
+      </c>
+      <c r="C16" s="4">
+        <v>500</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
       <c r="E16" s="1">
         <v>44</v>
       </c>
@@ -1255,9 +1321,15 @@
       <c r="A17" s="1">
         <v>15</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="1"/>
+      <c r="B17" s="3">
+        <v>46112</v>
+      </c>
+      <c r="C17" s="4">
+        <v>500</v>
+      </c>
+      <c r="D17" s="1">
+        <v>1</v>
+      </c>
       <c r="E17" s="1">
         <v>45</v>
       </c>

--- a/LoanOfficer-A/2026/162 angom bijenty.xlsx
+++ b/LoanOfficer-A/2026/162 angom bijenty.xlsx
@@ -819,7 +819,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>7500</v>
+        <v>9500</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>52500</v>
+        <v>50500</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1353,9 +1353,15 @@
       <c r="A18" s="1">
         <v>16</v>
       </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="1"/>
+      <c r="B18" s="3">
+        <v>46115</v>
+      </c>
+      <c r="C18" s="4">
+        <v>500</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
       <c r="E18" s="1">
         <v>46</v>
       </c>
@@ -1379,9 +1385,15 @@
       <c r="A19" s="1">
         <v>17</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="1"/>
+      <c r="B19" s="3">
+        <v>46117</v>
+      </c>
+      <c r="C19" s="4">
+        <v>500</v>
+      </c>
+      <c r="D19" s="1">
+        <v>1</v>
+      </c>
       <c r="E19" s="1">
         <v>47</v>
       </c>
@@ -1405,9 +1417,15 @@
       <c r="A20" s="1">
         <v>18</v>
       </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="1"/>
+      <c r="B20" s="3">
+        <v>46118</v>
+      </c>
+      <c r="C20" s="4">
+        <v>500</v>
+      </c>
+      <c r="D20" s="1">
+        <v>1</v>
+      </c>
       <c r="E20" s="1">
         <v>48</v>
       </c>
@@ -1431,9 +1449,15 @@
       <c r="A21" s="1">
         <v>19</v>
       </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="1"/>
+      <c r="B21" s="3">
+        <v>46150</v>
+      </c>
+      <c r="C21" s="4">
+        <v>500</v>
+      </c>
+      <c r="D21" s="1">
+        <v>1</v>
+      </c>
       <c r="E21" s="1">
         <v>49</v>
       </c>

--- a/LoanOfficer-A/2026/162 angom bijenty.xlsx
+++ b/LoanOfficer-A/2026/162 angom bijenty.xlsx
@@ -819,7 +819,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>9500</v>
+        <v>11000</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>50500</v>
+        <v>49000</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1481,9 +1481,15 @@
       <c r="A22" s="1">
         <v>20</v>
       </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="1"/>
+      <c r="B22" s="3">
+        <v>46165</v>
+      </c>
+      <c r="C22" s="4">
+        <v>500</v>
+      </c>
+      <c r="D22" s="1">
+        <v>1</v>
+      </c>
       <c r="E22" s="1">
         <v>50</v>
       </c>
@@ -1507,9 +1513,15 @@
       <c r="A23" s="1">
         <v>21</v>
       </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="1"/>
+      <c r="B23" s="3">
+        <v>46165</v>
+      </c>
+      <c r="C23" s="4">
+        <v>500</v>
+      </c>
+      <c r="D23" s="1">
+        <v>1</v>
+      </c>
       <c r="E23" s="1">
         <v>51</v>
       </c>
@@ -1533,9 +1545,15 @@
       <c r="A24" s="1">
         <v>22</v>
       </c>
-      <c r="B24" s="3"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="1"/>
+      <c r="B24" s="3">
+        <v>46168</v>
+      </c>
+      <c r="C24" s="4">
+        <v>500</v>
+      </c>
+      <c r="D24" s="1">
+        <v>1</v>
+      </c>
       <c r="E24" s="1">
         <v>52</v>
       </c>

--- a/LoanOfficer-A/2026/162 angom bijenty.xlsx
+++ b/LoanOfficer-A/2026/162 angom bijenty.xlsx
@@ -819,7 +819,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>11000</v>
+        <v>12500</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>49000</v>
+        <v>47500</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1577,9 +1577,15 @@
       <c r="A25" s="1">
         <v>23</v>
       </c>
-      <c r="B25" s="3"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="1"/>
+      <c r="B25" s="3">
+        <v>46174</v>
+      </c>
+      <c r="C25" s="4">
+        <v>500</v>
+      </c>
+      <c r="D25" s="1">
+        <v>1</v>
+      </c>
       <c r="E25" s="1">
         <v>53</v>
       </c>
@@ -1603,9 +1609,15 @@
       <c r="A26" s="1">
         <v>24</v>
       </c>
-      <c r="B26" s="3"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="1"/>
+      <c r="B26" s="3">
+        <v>46176</v>
+      </c>
+      <c r="C26" s="4">
+        <v>500</v>
+      </c>
+      <c r="D26" s="1">
+        <v>1</v>
+      </c>
       <c r="E26" s="1">
         <v>54</v>
       </c>
@@ -1629,9 +1641,15 @@
       <c r="A27" s="1">
         <v>25</v>
       </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="1"/>
+      <c r="B27" s="3">
+        <v>46177</v>
+      </c>
+      <c r="C27" s="4">
+        <v>500</v>
+      </c>
+      <c r="D27" s="1">
+        <v>1</v>
+      </c>
       <c r="E27" s="1">
         <v>55</v>
       </c>

--- a/LoanOfficer-A/2026/162 angom bijenty.xlsx
+++ b/LoanOfficer-A/2026/162 angom bijenty.xlsx
@@ -819,7 +819,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>12500</v>
+        <v>14000</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>47500</v>
+        <v>46000</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1673,9 +1673,15 @@
       <c r="A28" s="1">
         <v>26</v>
       </c>
-      <c r="B28" s="3"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="1"/>
+      <c r="B28" s="3">
+        <v>46178</v>
+      </c>
+      <c r="C28" s="4">
+        <v>500</v>
+      </c>
+      <c r="D28" s="1">
+        <v>1</v>
+      </c>
       <c r="E28" s="1">
         <v>56</v>
       </c>
@@ -1699,9 +1705,15 @@
       <c r="A29" s="1">
         <v>27</v>
       </c>
-      <c r="B29" s="3"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="1"/>
+      <c r="B29" s="3">
+        <v>46179</v>
+      </c>
+      <c r="C29" s="4">
+        <v>500</v>
+      </c>
+      <c r="D29" s="1">
+        <v>1</v>
+      </c>
       <c r="E29" s="1">
         <v>57</v>
       </c>
@@ -1725,9 +1737,15 @@
       <c r="A30" s="1">
         <v>28</v>
       </c>
-      <c r="B30" s="3"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="1"/>
+      <c r="B30" s="3">
+        <v>46182</v>
+      </c>
+      <c r="C30" s="4">
+        <v>500</v>
+      </c>
+      <c r="D30" s="1">
+        <v>1</v>
+      </c>
       <c r="E30" s="1">
         <v>58</v>
       </c>
